--- a/output/pdf_financials_xlsx/CASC.xlsx
+++ b/output/pdf_financials_xlsx/CASC.xlsx
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.171579</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.213765</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.347406</v>
       </c>
     </row>
     <row r="93">
@@ -3071,7 +3071,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3486,7 +3490,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.171579</v>
       </c>

--- a/output/pdf_financials_xlsx/CASC.xlsx
+++ b/output/pdf_financials_xlsx/CASC.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008142</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001846</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006489999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.370452</v>
+        <v>-0.378594</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.416511</v>
+        <v>-0.418357</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.429181</v>
+        <v>-0.42983</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.370452</v>
+        <v>-0.378594</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.416511</v>
+        <v>-0.418357</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.429181</v>
+        <v>-0.42983</v>
       </c>
     </row>
     <row r="30">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">

--- a/output/pdf_financials_xlsx/CASC.xlsx
+++ b/output/pdf_financials_xlsx/CASC.xlsx
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.08377900000000001</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.077387</v>
       </c>
     </row>
     <row r="65">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0266</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.037113</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.029624</v>
       </c>
     </row>
     <row r="68">
@@ -3901,7 +3901,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>1</v>
       </c>
